--- a/运营商毛利占比_2025年.xlsx
+++ b/运营商毛利占比_2025年.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="运营商毛利占比_2025年" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,30 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +56,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,429 +439,539 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>公司</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>运营商毛利(万元)</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>营业毛利(万元)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>运营商占比%</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>运营商收入(万元)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>运营商成本(万元)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>上海</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>2557.38</v>
-      </c>
-      <c r="C2" t="n">
-        <v>6445.35</v>
-      </c>
-      <c r="D2" t="n">
-        <v>39.68</v>
+      <c r="B2" s="3" t="n">
+        <v>2588.86</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>7201.17</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>35.95</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>3573.35</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>984.49</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1866.09</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>7839.67</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>3230.45</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>1364.37</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>广东</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>1711.45</v>
-      </c>
-      <c r="C3" t="n">
-        <v>5778.78</v>
-      </c>
-      <c r="D3" t="n">
-        <v>29.62</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>北京</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1581.02</v>
-      </c>
-      <c r="C4" t="n">
-        <v>8010.25</v>
-      </c>
-      <c r="D4" t="n">
-        <v>19.74</v>
+      <c r="B4" s="3" t="n">
+        <v>1787.16</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>6425.62</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>3282.28</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1495.12</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>辽宁</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1067.54</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>2680.91</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>39.82</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>2605.91</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1538.37</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>安徽</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>772.8099999999999</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2875.24</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>885.76</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>112.95</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>山西</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>767.58</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>2024.5</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>930.36</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>162.78</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>河南</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>635.3099999999999</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>5678.13</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>11.19</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1585.48</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>950.17</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>四川</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>556.05</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>2077.39</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1419.45</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>863.4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>湖北</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>460.36</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1230.78</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>561.59</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>101.23</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>江苏</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>278.32</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>654.59</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>42.52</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>282.47</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>4.15</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>宁波</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>812.77</v>
-      </c>
-      <c r="C5" t="n">
-        <v>1845.36</v>
-      </c>
-      <c r="D5" t="n">
-        <v>44.04</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>四川</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>766.27</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2803.55</v>
-      </c>
-      <c r="D6" t="n">
-        <v>27.33</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>安徽</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>761.12</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2594.84</v>
-      </c>
-      <c r="D7" t="n">
-        <v>29.33</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>辽宁</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>742.62</v>
-      </c>
-      <c r="C8" t="n">
-        <v>2485.4</v>
-      </c>
-      <c r="D8" t="n">
-        <v>29.88</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>山西</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>620.1799999999999</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2263.77</v>
-      </c>
-      <c r="D9" t="n">
-        <v>27.4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>河南</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>510.86</v>
-      </c>
-      <c r="C10" t="n">
-        <v>6304.87</v>
-      </c>
-      <c r="D10" t="n">
-        <v>8.1</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>湖北</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>499.57</v>
-      </c>
-      <c r="C11" t="n">
-        <v>1513.81</v>
-      </c>
-      <c r="D11" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="B12" s="3" t="n">
+        <v>268.61</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1562.61</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>17.19</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1187.39</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>918.78</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>云南</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>201.72</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1145.02</v>
-      </c>
-      <c r="D12" t="n">
-        <v>17.62</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="B13" s="3" t="n">
+        <v>193.04</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1299.94</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>461.29</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>268.25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>陕西</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>177.52</v>
-      </c>
-      <c r="C13" t="n">
-        <v>2357.8</v>
-      </c>
-      <c r="D13" t="n">
-        <v>7.53</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="B14" s="3" t="n">
+        <v>134.95</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>2326.27</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>327.84</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>192.88</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>379.09</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>27.45</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>湖南</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>73.20999999999999</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>961.99</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>257.55</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>184.34</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>河北</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>1018.12</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>珠海</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>143.09</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3366.78</v>
-      </c>
-      <c r="D14" t="n">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>江苏迪丰</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>140.96</v>
-      </c>
-      <c r="C15" t="n">
-        <v>531.88</v>
-      </c>
-      <c r="D15" t="n">
-        <v>26.5</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="B18" s="3" t="n">
+        <v>40.11</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>927.73</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>43.65</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>663.34</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>26.85</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>福建</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>133.07</v>
-      </c>
-      <c r="C16" t="n">
-        <v>1087.72</v>
-      </c>
-      <c r="D16" t="n">
-        <v>12.23</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>湖南</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>124.89</v>
-      </c>
-      <c r="C17" t="n">
-        <v>913.67</v>
-      </c>
-      <c r="D17" t="n">
-        <v>13.67</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>江苏</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>90.26000000000001</v>
-      </c>
-      <c r="C18" t="n">
-        <v>178.38</v>
-      </c>
-      <c r="D18" t="n">
-        <v>50.6</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>重庆</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>67.65000000000001</v>
-      </c>
-      <c r="C19" t="n">
-        <v>416.38</v>
-      </c>
-      <c r="D19" t="n">
-        <v>16.25</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>温州</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>55.26</v>
-      </c>
-      <c r="C20" t="n">
-        <v>133.21</v>
-      </c>
-      <c r="D20" t="n">
-        <v>41.48</v>
+      <c r="B20" s="3" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>291.2</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>3.16</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>河北</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>41.42</v>
-      </c>
-      <c r="C21" t="n">
-        <v>958.42</v>
-      </c>
-      <c r="D21" t="n">
-        <v>4.32</v>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>甘肃</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>161.41</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>6.24</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>江西</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>202.53</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>山东</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="C22" t="n">
-        <v>2925.19</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>甘肃</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>9.08</v>
-      </c>
-      <c r="C23" t="n">
-        <v>202.01</v>
-      </c>
-      <c r="D23" t="n">
-        <v>4.49</v>
+      <c r="B23" s="3" t="n">
+        <v>-21.9</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>3402.32</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-0.64</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>572.29</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>594.2</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>天津</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>8</v>
-      </c>
-      <c r="C24" t="n">
-        <v>600.33</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>贵州</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="C25" t="n">
-        <v>44.3</v>
-      </c>
-      <c r="D25" t="n">
-        <v>11.15</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>11770.4</v>
-      </c>
-      <c r="C26" t="n">
-        <v>54907.07</v>
-      </c>
-      <c r="D26" t="n">
-        <v>21.44</v>
+      <c r="B24" s="4" t="n">
+        <v>11678.83</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>51884.55</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>22.51</v>
       </c>
     </row>
   </sheetData>
